--- a/reconcile/storage/output/filtered_projects.xlsx
+++ b/reconcile/storage/output/filtered_projects.xlsx
@@ -30172,7 +30172,7 @@
         </is>
       </c>
       <c r="K386" t="n">
-        <v>9.125</v>
+        <v>9125</v>
       </c>
       <c r="L386" t="inlineStr">
         <is>

--- a/reconcile/storage/output/filtered_projects.xlsx
+++ b/reconcile/storage/output/filtered_projects.xlsx
@@ -1118,7 +1118,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>gigawatt hour</t>
+          <t>gigawatt</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -3677,14 +3677,8 @@
           <t>battery assembly</t>
         </is>
       </c>
-      <c r="K42" t="n">
-        <v>30</v>
-      </c>
-      <c r="L42" t="inlineStr">
-        <is>
-          <t>gigawatt hour</t>
-        </is>
-      </c>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
       <c r="M42" t="inlineStr">
         <is>
           <t>announced</t>
@@ -5109,14 +5103,8 @@
           <t>large-scale stationary storage systems</t>
         </is>
       </c>
-      <c r="K61" t="n">
-        <v>0.025</v>
-      </c>
-      <c r="L61" t="inlineStr">
-        <is>
-          <t>gigawatt hour</t>
-        </is>
-      </c>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
       <c r="M61" t="inlineStr">
         <is>
           <t>operational</t>
@@ -5190,11 +5178,11 @@
         </is>
       </c>
       <c r="K62" t="n">
-        <v>1.5</v>
+        <v>30000</v>
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>gigawatt hour</t>
+          <t>unit</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
@@ -5265,14 +5253,8 @@
           <t>lithium-ion batteries</t>
         </is>
       </c>
-      <c r="K63" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="L63" t="inlineStr">
-        <is>
-          <t>gigawatt hour</t>
-        </is>
-      </c>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
       <c r="M63" t="inlineStr">
         <is>
           <t>operational</t>
@@ -5341,14 +5323,8 @@
           <t>high-voltage batteries</t>
         </is>
       </c>
-      <c r="K64" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="L64" t="inlineStr">
-        <is>
-          <t>gigawatt hour</t>
-        </is>
-      </c>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr"/>
       <c r="M64" t="inlineStr">
         <is>
           <t>announced</t>
@@ -5417,14 +5393,8 @@
           <t>high-voltage batteries</t>
         </is>
       </c>
-      <c r="K65" t="n">
-        <v>5</v>
-      </c>
-      <c r="L65" t="inlineStr">
-        <is>
-          <t>gigawatt hour</t>
-        </is>
-      </c>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr"/>
       <c r="M65" t="inlineStr">
         <is>
           <t>announced</t>
@@ -5497,14 +5467,8 @@
           <t>battery modules</t>
         </is>
       </c>
-      <c r="K66" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="L66" t="inlineStr">
-        <is>
-          <t>gigawatt hour</t>
-        </is>
-      </c>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr"/>
       <c r="M66" t="inlineStr">
         <is>
           <t>operational</t>
@@ -5577,14 +5541,8 @@
           <t>battery modules</t>
         </is>
       </c>
-      <c r="K67" t="n">
-        <v>5</v>
-      </c>
-      <c r="L67" t="inlineStr">
-        <is>
-          <t>gigawatt hour</t>
-        </is>
-      </c>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
       <c r="M67" t="inlineStr">
         <is>
           <t>announced</t>
@@ -7106,7 +7064,7 @@
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>gigawatt hour</t>
+          <t>gigawatt</t>
         </is>
       </c>
       <c r="M87" t="inlineStr">
@@ -12727,14 +12685,8 @@
           <t>battery module</t>
         </is>
       </c>
-      <c r="K161" t="n">
-        <v>0.0025</v>
-      </c>
-      <c r="L161" t="inlineStr">
-        <is>
-          <t>gigawatt hour</t>
-        </is>
-      </c>
+      <c r="K161" t="inlineStr"/>
+      <c r="L161" t="inlineStr"/>
       <c r="M161" t="inlineStr">
         <is>
           <t>operational</t>
@@ -12807,14 +12759,8 @@
           <t>battery pack</t>
         </is>
       </c>
-      <c r="K162" t="n">
-        <v>0.0025</v>
-      </c>
-      <c r="L162" t="inlineStr">
-        <is>
-          <t>gigawatt hour</t>
-        </is>
-      </c>
+      <c r="K162" t="inlineStr"/>
+      <c r="L162" t="inlineStr"/>
       <c r="M162" t="inlineStr">
         <is>
           <t>operational</t>
@@ -14132,11 +14078,11 @@
         </is>
       </c>
       <c r="K179" t="n">
-        <v>6.75</v>
+        <v>135000</v>
       </c>
       <c r="L179" t="inlineStr">
         <is>
-          <t>gigawatt hour</t>
+          <t>unit</t>
         </is>
       </c>
       <c r="M179" t="inlineStr">
@@ -14524,7 +14470,7 @@
       </c>
       <c r="L184" t="inlineStr">
         <is>
-          <t>gigawatt hour</t>
+          <t>tonne</t>
         </is>
       </c>
       <c r="M184" t="inlineStr">
@@ -19735,14 +19681,8 @@
           <t>battery housings</t>
         </is>
       </c>
-      <c r="K251" t="n">
-        <v>15</v>
-      </c>
-      <c r="L251" t="inlineStr">
-        <is>
-          <t>gigawatt hour</t>
-        </is>
-      </c>
+      <c r="K251" t="inlineStr"/>
+      <c r="L251" t="inlineStr"/>
       <c r="M251" t="inlineStr">
         <is>
           <t>announced</t>
@@ -30099,14 +30039,8 @@
           <t>battery recycling</t>
         </is>
       </c>
-      <c r="K385" t="n">
-        <v>9125</v>
-      </c>
-      <c r="L385" t="inlineStr">
-        <is>
-          <t>gigawatt hour</t>
-        </is>
-      </c>
+      <c r="K385" t="inlineStr"/>
+      <c r="L385" t="inlineStr"/>
       <c r="M385" t="inlineStr">
         <is>
           <t>operational</t>
@@ -30572,7 +30506,7 @@
       </c>
       <c r="L391" t="inlineStr">
         <is>
-          <t>gigawatt hour</t>
+          <t>tonne</t>
         </is>
       </c>
       <c r="M391" t="inlineStr">
@@ -30793,14 +30727,8 @@
           <t>lithium-ion batteries</t>
         </is>
       </c>
-      <c r="K394" t="n">
-        <v>15</v>
-      </c>
-      <c r="L394" t="inlineStr">
-        <is>
-          <t>gigawatt hour</t>
-        </is>
-      </c>
+      <c r="K394" t="inlineStr"/>
+      <c r="L394" t="inlineStr"/>
       <c r="M394" t="inlineStr">
         <is>
           <t>announced</t>
@@ -34269,14 +34197,8 @@
           <t>battery modules</t>
         </is>
       </c>
-      <c r="K438" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L438" t="inlineStr">
-        <is>
-          <t>gigawatt hour</t>
-        </is>
-      </c>
+      <c r="K438" t="inlineStr"/>
+      <c r="L438" t="inlineStr"/>
       <c r="M438" t="inlineStr">
         <is>
           <t>announced</t>
@@ -35030,7 +34952,7 @@
       </c>
       <c r="L448" t="inlineStr">
         <is>
-          <t>gigawatt hour</t>
+          <t>gigawatt</t>
         </is>
       </c>
       <c r="M448" t="inlineStr">
@@ -35254,7 +35176,7 @@
       </c>
       <c r="L451" t="inlineStr">
         <is>
-          <t>gigawatt hour</t>
+          <t>tonne</t>
         </is>
       </c>
       <c r="M451" t="inlineStr">
@@ -36319,14 +36241,8 @@
           <t>LFP Battery Cell</t>
         </is>
       </c>
-      <c r="K465" t="n">
-        <v>5000</v>
-      </c>
-      <c r="L465" t="inlineStr">
-        <is>
-          <t>gigawatt hour</t>
-        </is>
-      </c>
+      <c r="K465" t="inlineStr"/>
+      <c r="L465" t="inlineStr"/>
       <c r="M465" t="inlineStr">
         <is>
           <t>announced</t>
@@ -38075,9 +37991,7 @@
           <t>300 mm wafers</t>
         </is>
       </c>
-      <c r="K489" t="n">
-        <v>480000</v>
-      </c>
+      <c r="K489" t="inlineStr"/>
       <c r="L489" t="inlineStr"/>
       <c r="M489" t="inlineStr">
         <is>
@@ -40554,7 +40468,7 @@
       </c>
       <c r="L523" t="inlineStr">
         <is>
-          <t>gigawatt hour</t>
+          <t>tonne</t>
         </is>
       </c>
       <c r="M523" t="inlineStr">
@@ -40777,14 +40691,8 @@
           <t>pouch cells</t>
         </is>
       </c>
-      <c r="K526" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="L526" t="inlineStr">
-        <is>
-          <t>gigawatt hour</t>
-        </is>
-      </c>
+      <c r="K526" t="inlineStr"/>
+      <c r="L526" t="inlineStr"/>
       <c r="M526" t="inlineStr">
         <is>
           <t>announced</t>
@@ -47453,14 +47361,8 @@
           <t>battery packs</t>
         </is>
       </c>
-      <c r="K613" t="n">
-        <v>240</v>
-      </c>
-      <c r="L613" t="inlineStr">
-        <is>
-          <t>gigawatt hour</t>
-        </is>
-      </c>
+      <c r="K613" t="inlineStr"/>
+      <c r="L613" t="inlineStr"/>
       <c r="M613" t="inlineStr">
         <is>
           <t>under construction</t>
@@ -47529,14 +47431,8 @@
           <t>battery packs</t>
         </is>
       </c>
-      <c r="K614" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="L614" t="inlineStr">
-        <is>
-          <t>gigawatt hour</t>
-        </is>
-      </c>
+      <c r="K614" t="inlineStr"/>
+      <c r="L614" t="inlineStr"/>
       <c r="M614" t="inlineStr">
         <is>
           <t>announced</t>
@@ -48805,14 +48701,8 @@
           <t>battery cells</t>
         </is>
       </c>
-      <c r="K630" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="L630" t="inlineStr">
-        <is>
-          <t>gigawatt hour</t>
-        </is>
-      </c>
+      <c r="K630" t="inlineStr"/>
+      <c r="L630" t="inlineStr"/>
       <c r="M630" t="inlineStr">
         <is>
           <t>operational</t>
@@ -48885,14 +48775,8 @@
           <t>battery cells</t>
         </is>
       </c>
-      <c r="K631" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="L631" t="inlineStr">
-        <is>
-          <t>gigawatt hour</t>
-        </is>
-      </c>
+      <c r="K631" t="inlineStr"/>
+      <c r="L631" t="inlineStr"/>
       <c r="M631" t="inlineStr">
         <is>
           <t>operational</t>
@@ -51299,14 +51183,8 @@
           <t>e-bike batteries</t>
         </is>
       </c>
-      <c r="K662" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="L662" t="inlineStr">
-        <is>
-          <t>gigawatt hour</t>
-        </is>
-      </c>
+      <c r="K662" t="inlineStr"/>
+      <c r="L662" t="inlineStr"/>
       <c r="M662" t="inlineStr">
         <is>
           <t>operational</t>
